--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/30,06,26 ПОКОМ КИ/дв 30,06,26 бррсч пок ки (нет заказа).xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/30,06,26 ПОКОМ КИ/дв 30,06,26 бррсч пок ки (нет заказа).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчет ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\06,26\30,06,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB9CDAA-4837-4BC7-AF2C-3421D575494C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{847C869E-0BE0-4220-973E-5A54566C1031}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AE$114</definedName>
   </definedNames>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="262">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -807,6 +815,9 @@
   <si>
     <t>нет</t>
   </si>
+  <si>
+    <t>ВНИМАНИЕ / P005156</t>
+  </si>
 </sst>
 </file>
 
@@ -10940,8 +10951,8 @@
         <v>1</v>
       </c>
       <c r="H90" s="1"/>
-      <c r="I90" s="1" t="s">
-        <v>208</v>
+      <c r="I90" s="17" t="s">
+        <v>261</v>
       </c>
       <c r="J90" s="1"/>
       <c r="K90" s="1">
